--- a/excels/sample_verbal_questions.xlsx
+++ b/excels/sample_verbal_questions.xlsx
@@ -519,6 +519,11 @@
           <t>Question Images</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Answer Images</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -583,7 +588,7 @@
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="n"/>
+      <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="n"/>
     </row>
     <row r="3">
@@ -649,7 +654,7 @@
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="n"/>
+      <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="n"/>
     </row>
     <row r="4">
@@ -703,7 +708,7 @@
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="n"/>
+      <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="n"/>
     </row>
     <row r="5">
@@ -765,7 +770,7 @@
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="n"/>
+      <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="n"/>
     </row>
     <row r="6">
@@ -831,7 +836,7 @@
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="n"/>
+      <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="n"/>
     </row>
     <row r="7">
@@ -897,7 +902,7 @@
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="n"/>
+      <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="n"/>
     </row>
     <row r="8">
@@ -1045,7 +1050,7 @@
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="n"/>
+      <c r="O9" s="2" t="inlineStr"/>
       <c r="P9" s="2" t="n"/>
     </row>
     <row r="10">
@@ -1111,7 +1116,7 @@
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="n"/>
+      <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="n"/>
     </row>
     <row r="11">
@@ -1177,7 +1182,7 @@
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="n"/>
+      <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="n"/>
     </row>
   </sheetData>
